--- a/Hardware/CMU BOM.xlsx
+++ b/Hardware/CMU BOM.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30889B3-FFD7-4E86-AEBF-3874D85A4068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946BBFC4-6B83-4DCD-9B1D-CF4EA669B07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="16200" windowHeight="9847" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="172">
   <si>
     <t>Qty</t>
   </si>
@@ -44,9 +43,6 @@
   </si>
   <si>
     <t>T1, T2</t>
-  </si>
-  <si>
-    <t>CEP99-102</t>
   </si>
   <si>
     <t>CEP99102</t>
@@ -647,10 +643,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -947,254 +943,254 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" ht="25.5">
-      <c r="A1" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
+      <c r="A1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4">
         <v>35</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="H3" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" s="4">
         <v>6</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="H4" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="4">
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="H5" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6" s="4">
         <v>10</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="H6" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="4">
         <v>1</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" s="4">
         <v>885382207008</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="H7" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="4">
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>78</v>
-      </c>
       <c r="H8" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="4">
         <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="H9" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4">
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" s="4">
         <v>885012207079</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="H10" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="4">
         <v>1</v>
@@ -1203,71 +1199,71 @@
         <v>2</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>86</v>
-      </c>
       <c r="H11" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4">
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12" s="4">
         <v>61300211121</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="H12" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="4">
         <v>2</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" s="4">
         <v>705510038</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>92</v>
-      </c>
       <c r="H13" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1278,22 +1274,22 @@
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" s="4">
         <v>61300211121</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="H14" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1304,308 +1300,308 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D15" s="4">
         <v>705550056</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="H15" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" s="4">
         <v>8</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D16" s="4">
         <v>61300211121</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="G16" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="4">
         <v>17</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="G17" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4">
         <v>8</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>140</v>
-      </c>
       <c r="H18" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4">
         <v>17</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>104</v>
-      </c>
       <c r="F19" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4">
         <v>4</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="F20" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="4">
         <v>4</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>108</v>
-      </c>
       <c r="F21" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4">
         <v>1</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="G22" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4">
         <v>1</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>112</v>
-      </c>
       <c r="F23" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4">
         <v>1</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="F24" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D25" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="F25" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" s="4">
         <v>8</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="F26" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G26" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1616,98 +1612,98 @@
         <v>2</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="H27" s="7" t="s">
         <v>171</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" s="4">
         <v>2</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D28" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="G28" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G28" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="H28" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" s="4">
         <v>1</v>
       </c>
       <c r="C29" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="F29" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" s="4">
         <v>1</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="F30" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="H30" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:8">
